--- a/exemple-ePrescription/ig/StructureDefinition-fr-cda-reference-interne.xlsx
+++ b/exemple-ePrescription/ig/StructureDefinition-fr-cda-reference-interne.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-06T08:51:06+00:00</t>
+    <t>2026-05-06T11:50:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3774,7 +3774,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="27" hidden="true">
+    <row r="27">
       <c r="A27" t="s" s="2">
         <v>156</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>75</v>
       </c>
       <c r="H27" t="s" s="2">
-        <v>74</v>
+        <v>151</v>
       </c>
       <c r="I27" t="s" s="2">
         <v>74</v>
